--- a/Calc_Project_BOM.xlsx
+++ b/Calc_Project_BOM.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{23E78669-AB12-47AA-8CB1-E7B4FFFF5D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{65851F57-38D3-43A1-B309-FAD7F0E4E897}"/>
+    <workbookView xWindow="32910" yWindow="1560" windowWidth="17280" windowHeight="8880" xr2:uid="{65851F57-38D3-43A1-B309-FAD7F0E4E897}"/>
   </bookViews>
   <sheets>
     <sheet name="Calc_Project_BOM" sheetId="1" r:id="rId1"/>
